--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487159_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487159_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.1488</v>
+        <v>9.396100000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>6.339</v>
+        <v>7.5595</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8098</v>
+        <v>1.8366</v>
       </c>
       <c r="G2" t="n">
         <v>6.7682</v>
@@ -610,13 +610,13 @@
         <v>2.1231</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0054</v>
+        <v>0.2419</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8778</v>
+        <v>0.3428</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1276</v>
+        <v>-0.1008</v>
       </c>
       <c r="V2" t="n">
         <v>1.228</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2459</v>
+        <v>6.7618</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5919</v>
+        <v>5.6528</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6539</v>
+        <v>1.109</v>
       </c>
       <c r="G3" t="n">
         <v>3.6625</v>
@@ -688,13 +688,13 @@
         <v>2.1231</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8256</v>
+        <v>0.6904</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6848</v>
+        <v>0.3761</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1408</v>
+        <v>0.3143</v>
       </c>
       <c r="V3" t="n">
         <v>0.2859</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. CARPINTERO REVILLA</t>
+          <t>J. JORGE RODRIGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3379</v>
+        <v>4.049</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5356</v>
+        <v>1.0838</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8023</v>
+        <v>2.9652</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6921</v>
+        <v>2.283</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3821</v>
+        <v>2.8649</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0742</v>
+        <v>-0.5819</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1114</v>
+        <v>2.7233</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2325</v>
+        <v>3.2859</v>
       </c>
       <c r="L4" t="n">
-        <v>0.879</v>
+        <v>-0.5626</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5806</v>
+        <v>-0.4403</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6146</v>
+        <v>-0.421</v>
       </c>
       <c r="O4" t="n">
-        <v>1.1953</v>
+        <v>-0.0193</v>
       </c>
       <c r="P4" t="n">
-        <v>0.965</v>
+        <v>1.3511</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R4" t="n">
-        <v>2.8951</v>
+        <v>3.2811</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6228</v>
+        <v>-0.2413</v>
       </c>
       <c r="T4" t="n">
-        <v>3.0684</v>
+        <v>0.2905</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4455</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9421</v>
+        <v>0.6562</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.228</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. JORGE RODRIGUEZ</t>
+          <t>F. AMBROSONI ÁLVAREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0813</v>
+        <v>2.9584</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4641</v>
+        <v>1.834</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6172</v>
+        <v>1.1244</v>
       </c>
       <c r="G5" t="n">
-        <v>2.283</v>
+        <v>-1.9711</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8649</v>
+        <v>0.5072</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5819</v>
+        <v>-2.4783</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7233</v>
+        <v>-1.6847</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2859</v>
+        <v>0.3674</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5626</v>
+        <v>-2.0521</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4403</v>
+        <v>-0.2864</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.421</v>
+        <v>0.1399</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0193</v>
+        <v>-0.4263</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3511</v>
+        <v>1.7371</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9301</v>
+        <v>-0.193</v>
       </c>
       <c r="R5" t="n">
-        <v>3.2811</v>
+        <v>1.9301</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2089</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3291</v>
+        <v>0.0278</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8798</v>
+        <v>-0.5615</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6562</v>
+        <v>3.7261</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.6839</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6562</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. AMBROSONI ÁLVAREZ</t>
+          <t>E. CARPINTERO REVILLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7115</v>
+        <v>2.461</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7745</v>
+        <v>0.5516</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9370000000000001</v>
+        <v>1.9093</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.9711</v>
+        <v>1.6921</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5072</v>
+        <v>-0.3821</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.4783</v>
+        <v>2.0742</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.6847</v>
+        <v>1.1114</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3674</v>
+        <v>0.2325</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.0521</v>
+        <v>0.879</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2864</v>
+        <v>0.5806</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1399</v>
+        <v>-0.6146</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4263</v>
+        <v>1.1953</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7371</v>
+        <v>0.965</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.193</v>
+        <v>-1.9301</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9301</v>
+        <v>2.8951</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7806</v>
+        <v>0.7459</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0317</v>
+        <v>1.0844</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7489</v>
+        <v>-0.3385</v>
       </c>
       <c r="V6" t="n">
-        <v>3.7261</v>
+        <v>-0.9421</v>
       </c>
       <c r="W6" t="n">
-        <v>3.6839</v>
+        <v>0.2859</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0422</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3638</v>
+        <v>0.5072</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4125</v>
+        <v>1.1716</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0487</v>
+        <v>-0.6644</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1046</v>
@@ -1000,13 +1000,13 @@
         <v>1.5441</v>
       </c>
       <c r="S7" t="n">
-        <v>1.7893</v>
+        <v>0.9326</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7549</v>
+        <v>0.5139</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0344</v>
+        <v>0.4187</v>
       </c>
       <c r="V7" t="n">
         <v>-0.8999</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.28</v>
+        <v>-0.046</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4036</v>
+        <v>-1.3035</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1236</v>
+        <v>1.2574</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5289</v>
@@ -1078,13 +1078,13 @@
         <v>0.772</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0443</v>
+        <v>0.1897</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0132</v>
+        <v>0.1134</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0575</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2859</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9520999999999999</v>
+        <v>-0.8718</v>
       </c>
       <c r="E9" t="n">
         <v>-0.5729</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3793</v>
+        <v>-0.299</v>
       </c>
       <c r="G9" t="n">
         <v>-1.2743</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0059</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="T9" t="n">
         <v>0.074</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.08</v>
+        <v>0.0003</v>
       </c>
       <c r="V9" t="n">
         <v>0.3281</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. HERNANDEZ HERNANDEZ</t>
+          <t>A. REYES ABAD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3152</v>
+        <v>-2.9179</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3457</v>
+        <v>-2.7458</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0305</v>
+        <v>-0.1721</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3263</v>
+        <v>-1.2704</v>
       </c>
       <c r="H10" t="n">
-        <v>0.03</v>
+        <v>-0.3715</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3563</v>
+        <v>-0.8989</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1671</v>
+        <v>0.0171</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0364</v>
+        <v>-0.5848</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2035</v>
+        <v>0.6019</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4934</v>
+        <v>-1.2875</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0664</v>
+        <v>0.2134</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5598</v>
+        <v>-1.5009</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.6672</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.9833</v>
+        <v>-3.0881</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3161</v>
+        <v>0.965</v>
       </c>
       <c r="S10" t="n">
-        <v>2.636</v>
+        <v>0.1897</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1845</v>
+        <v>0.0393</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4515</v>
+        <v>0.1504</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0422</v>
+        <v>0.2859</v>
       </c>
       <c r="W10" t="n">
         <v>0.2859</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2436</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. KEITH CAMARA</t>
+          <t>O. HERNANDEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2477</v>
+        <v>-3.0741</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.072</v>
+        <v>-5.0874</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8243</v>
+        <v>2.0133</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8602</v>
+        <v>-0.3263</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.08690000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7733</v>
+        <v>-0.3563</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6269</v>
+        <v>0.1671</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-0.0364</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6269</v>
+        <v>0.2035</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2333</v>
+        <v>-0.4934</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.08690000000000001</v>
+        <v>0.0664</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1464</v>
+        <v>-0.5598</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.7371</v>
+        <v>-3.6672</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.0881</v>
+        <v>-5.9833</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3511</v>
+        <v>2.3161</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6504</v>
+        <v>0.8771</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3569</v>
+        <v>0.4429</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2935</v>
+        <v>0.4342</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.0422</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.2436</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. REYES ABAD</t>
+          <t>D. KEITH CAMARA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5525</v>
+        <v>-3.087</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2465</v>
+        <v>-4.072</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.306</v>
+        <v>0.9849</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.2704</v>
+        <v>-0.8602</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3715</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8989</v>
+        <v>-0.7733</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0171</v>
+        <v>-0.6269</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5848</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6019</v>
+        <v>-0.6269</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2875</v>
+        <v>-0.2333</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2134</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.5009</v>
+        <v>-0.1464</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.1231</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q12" t="n">
         <v>-3.0881</v>
       </c>
       <c r="R12" t="n">
-        <v>0.965</v>
+        <v>1.3511</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4449</v>
+        <v>-0.4898</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4614</v>
+        <v>-0.3569</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0165</v>
+        <v>-0.1329</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>15.5417</v>
+        <v>16.1367</v>
       </c>
       <c r="E13" t="n">
-        <v>3.476900000000001</v>
+        <v>4.071699999999999</v>
       </c>
       <c r="F13" t="n">
         <v>12.0646</v>
@@ -1447,7 +1447,7 @@
         <v>3.8749</v>
       </c>
       <c r="L13" t="n">
-        <v>7.7294</v>
+        <v>7.729400000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-3.5344</v>
@@ -1459,7 +1459,7 @@
         <v>-1.5281</v>
       </c>
       <c r="P13" t="n">
-        <v>0.964900000000001</v>
+        <v>0.9649000000000003</v>
       </c>
       <c r="Q13" t="n">
         <v>-18.3357</v>
@@ -1468,13 +1468,13 @@
         <v>19.3008</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0821</v>
+        <v>2.6768</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3533</v>
+        <v>2.948199999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2711999999999999</v>
+        <v>-0.2713000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>4.4245</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6609</v>
+        <v>3.5263</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4362</v>
+        <v>1.0342</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2247</v>
+        <v>2.492</v>
       </c>
       <c r="G14" t="n">
         <v>0.1001</v>
@@ -1546,13 +1546,13 @@
         <v>2.7021</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0312</v>
+        <v>0.8966</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2223</v>
+        <v>0.8203</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.191</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>1.7575</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7478</v>
+        <v>3.1411</v>
       </c>
       <c r="E15" t="n">
-        <v>0.445</v>
+        <v>0.9457</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3028</v>
+        <v>2.1954</v>
       </c>
       <c r="G15" t="n">
         <v>1.6405</v>
@@ -1624,13 +1624,13 @@
         <v>3.0881</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2122</v>
+        <v>0.6055</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3291</v>
+        <v>0.1716</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5413</v>
+        <v>0.4339</v>
       </c>
       <c r="V15" t="n">
         <v>-1.228</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0254</v>
+        <v>0.3992</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3714</v>
+        <v>0.0291</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3968</v>
+        <v>0.37</v>
       </c>
       <c r="G16" t="n">
         <v>0.4992</v>
@@ -1702,13 +1702,13 @@
         <v>1.158</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4039</v>
+        <v>-0.0301</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4164</v>
+        <v>-0.0159</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0126</v>
+        <v>-0.0142</v>
       </c>
       <c r="V16" t="n">
         <v>-1.228</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. JUSTO ANTOLIN</t>
+          <t>A. KARATZAS LACABEX</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0239</v>
+        <v>-0.2911</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8798</v>
+        <v>2.3145</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9038</v>
+        <v>-2.6056</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4996</v>
+        <v>-0.493</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.7781</v>
+        <v>0.9201</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2785</v>
+        <v>-1.413</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4689</v>
+        <v>2.2488</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7763</v>
+        <v>1.7283</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2453</v>
+        <v>0.5205</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.9685</v>
+        <v>-2.7418</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0018</v>
+        <v>-0.8082</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9668</v>
+        <v>-1.9336</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3511</v>
+        <v>1.5441</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3511</v>
+        <v>1.5441</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4105</v>
+        <v>-0.8127</v>
       </c>
       <c r="T17" t="n">
-        <v>1.125</v>
+        <v>-0.5483</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7145</v>
+        <v>-0.2644</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2859</v>
+        <v>-0.5295</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2859</v>
+        <v>0.614</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5717</v>
+        <v>-1.1435</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. KARATZAS LACABEX</t>
+          <t>A. JUSTO ANTOLIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2174</v>
+        <v>-0.3505</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4147</v>
+        <v>1.1789</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.6321</v>
+        <v>-1.5293</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.493</v>
+        <v>-1.4996</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9201</v>
+        <v>-1.7781</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.413</v>
+        <v>0.2785</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2488</v>
+        <v>0.4689</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7283</v>
+        <v>-0.7763</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5205</v>
+        <v>1.2453</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.7418</v>
+        <v>-1.9685</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8082</v>
+        <v>-1.0018</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.9336</v>
+        <v>-0.9668</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5441</v>
+        <v>1.3511</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5441</v>
+        <v>1.3511</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.739</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4481</v>
+        <v>0.4241</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2909</v>
+        <v>-0.3401</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5295</v>
+        <v>-0.2859</v>
       </c>
       <c r="W18" t="n">
-        <v>0.614</v>
+        <v>0.2859</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1435</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9485</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="E19" t="n">
         <v>-0.601</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3475</v>
+        <v>-0.214</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2328</v>
@@ -1936,13 +1936,13 @@
         <v>0.193</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2525</v>
+        <v>-0.119</v>
       </c>
       <c r="T19" t="n">
         <v>0.0145</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.267</v>
+        <v>-0.1335</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6562</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9599</v>
+        <v>-0.8263</v>
       </c>
       <c r="E20" t="n">
         <v>-0.6124000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3475</v>
+        <v>-0.214</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9004</v>
@@ -2014,13 +2014,13 @@
         <v>0.193</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2525</v>
+        <v>-0.119</v>
       </c>
       <c r="T20" t="n">
         <v>0.0145</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.267</v>
+        <v>-0.1335</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6574</v>
+        <v>-1.2836</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2822</v>
+        <v>-2.8816</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6248</v>
+        <v>1.598</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4465</v>
@@ -2092,13 +2092,13 @@
         <v>1.158</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4039</v>
+        <v>-0.0301</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4164</v>
+        <v>-0.0159</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0126</v>
+        <v>-0.0142</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5334</v>
+        <v>-1.6113</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.007</v>
+        <v>-3.4062</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4737</v>
+        <v>1.7949</v>
       </c>
       <c r="G22" t="n">
         <v>0.5191</v>
@@ -2170,13 +2170,13 @@
         <v>2.1231</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3154</v>
+        <v>-0.3933</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9518</v>
+        <v>-0.351</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3636</v>
+        <v>-0.0423</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6781</v>
+        <v>-4.581</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4326</v>
+        <v>-3.9333</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2455</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-2.5797</v>
@@ -2248,13 +2248,13 @@
         <v>2.3161</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1442</v>
+        <v>0.2413</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6637</v>
+        <v>0.163</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4805</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6985</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.7594</v>
+        <v>-5.145</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8213</v>
+        <v>-2.4207</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.9381</v>
+        <v>-2.7243</v>
       </c>
       <c r="G24" t="n">
         <v>-1.5157</v>
@@ -2326,13 +2326,13 @@
         <v>1.158</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5646</v>
+        <v>-0.9502</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8778</v>
+        <v>-0.4772</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6868</v>
+        <v>-0.473</v>
       </c>
       <c r="V24" t="n">
         <v>-0.9421</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.1978</v>
+        <v>-6.3692</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.1125</v>
+        <v>-3.712</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.0852</v>
+        <v>-2.6572</v>
       </c>
       <c r="G25" t="n">
         <v>-2.1611</v>
@@ -2404,13 +2404,13 @@
         <v>1.3511</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9485</v>
+        <v>-0.12</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3291</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6194</v>
+        <v>-0.1914</v>
       </c>
       <c r="V25" t="n">
         <v>-0.614</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-15.5417</v>
+        <v>-14.2064</v>
       </c>
       <c r="E26" t="n">
-        <v>-12.0647</v>
+        <v>-12.0648</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.4769</v>
+        <v>-2.141799999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-8.069899999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.868699999999999</v>
+        <v>-1.8687</v>
       </c>
       <c r="I26" t="n">
         <v>-6.2012</v>
@@ -2482,13 +2482,13 @@
         <v>18.3357</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.082199999999999</v>
+        <v>-0.747</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2713000000000004</v>
+        <v>0.2711000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.3532</v>
+        <v>-1.0181</v>
       </c>
       <c r="V26" t="n">
         <v>-4.4247</v>
